--- a/mobile/data/FleetAgent.xlsx
+++ b/mobile/data/FleetAgent.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FleetAttention" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FleetApprovals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FleetDecisions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FleetNotifications" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FleetHeartbeat" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetAttention" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetApprovals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetDecisions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetNotifications" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetHeartbeat" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1155,7 +1155,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="41" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>operator@example.com</t>
+          <t>mobile:operator@example.com</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>the decision expired before the laptop saw it decide again from the desk or the phone</t>
+          <t>the decision has expired, or expires later than fleet.mobile.expire_s allows decide again from the phone</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">

--- a/mobile/data/FleetAgent.xlsx
+++ b/mobile/data/FleetAgent.xlsx
@@ -1145,7 +1145,7 @@
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -1157,7 +1157,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="29" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="41" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
@@ -1461,7 +1461,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dpm-reports-pncli-write-20260925T110000Z-33be</t>
+          <t>dpm-reports-confluence-publish-20260925T110000Z-33be</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pncli-write</t>
+          <t>confluence-publish</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Publish the DPM-77 report to the production workspace</t>
+          <t>create page "DPM-77 weekly" in PROD (9120 chars)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{"truncated":true,"bytes":9120,"head":"{\"workspace\":\"Production\",\"report\":\"DPM-77 weekly\", ..."}</t>
+          <t>{"truncated":true,"bytes":9120,"head":"{\"space\":\"PROD\",\"title\":\"DPM-77 weekly\", ..."}</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Wrong workspace; retarget to UAT first.</t>
+          <t>Wrong space; publish to UAT first.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1554,7 +1554,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>dpm-reports-pncli-write-20260925T110000Z-33be.json</t>
+          <t>dpm-reports-confluence-publish-20260925T110000Z-33be.json</t>
         </is>
       </c>
     </row>
